--- a/OUTPUT/direct_P61611_Leptospira_interrogans_serovar_Copenhageni_str__Fiocruz_L1-130.xlsx
+++ b/OUTPUT/direct_P61611_Leptospira_interrogans_serovar_Copenhageni_str__Fiocruz_L1-130.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.2476</v>
+        <v>0.2477009196321471</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.2476</v>
+        <v>0.2477009196321471</v>
       </c>
     </row>
   </sheetData>
